--- a/project/outputs_xlsx_solution/prog-loop.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.2-wide.xlsx
@@ -65,7 +65,10 @@
     <t>fld F0, 0(X1)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
   </si>
   <si>
     <t>fmul F0, F0, F2</t>
@@ -74,10 +77,10 @@
     <t>fld F4, 0(X2)</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fadd F0, F0, F4</t>
@@ -86,6 +89,9 @@
     <t>fsd F0, 0(X2)</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>addi X1, X1, -8</t>
   </si>
   <si>
@@ -104,13 +110,37 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -555,6 +585,9 @@
       <c r="AC1">
         <v>26</v>
       </c>
+      <c r="AD1">
+        <v>27</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -576,7 +609,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -596,13 +629,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -645,13 +678,13 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -662,7 +695,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -671,22 +704,22 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -697,7 +730,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -706,16 +739,16 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +759,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -735,19 +768,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +791,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -767,13 +800,19 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="P9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>11</v>
       </c>
       <c r="R9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -784,7 +823,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -796,10 +835,10 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -810,7 +849,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -819,16 +858,16 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="T11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -839,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
@@ -848,16 +887,16 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="T12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -877,16 +916,16 @@
         <v>7</v>
       </c>
       <c r="O13" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="P13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="U13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -897,7 +936,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" t="s">
         <v>5</v>
@@ -906,22 +945,22 @@
         <v>7</v>
       </c>
       <c r="O14" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -932,7 +971,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N15" t="s">
         <v>5</v>
@@ -941,16 +980,16 @@
         <v>7</v>
       </c>
       <c r="P15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R15" t="s">
-        <v>13</v>
-      </c>
-      <c r="U15" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="V15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -961,7 +1000,7 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -970,19 +1009,19 @@
         <v>7</v>
       </c>
       <c r="P16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +1032,7 @@
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O17" t="s">
         <v>5</v>
@@ -1002,13 +1041,13 @@
         <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="X17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1019,7 +1058,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
         <v>5</v>
@@ -1028,16 +1067,16 @@
         <v>7</v>
       </c>
       <c r="Q18" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1048,7 +1087,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P19" t="s">
         <v>5</v>
@@ -1057,33 +1096,36 @@
         <v>7</v>
       </c>
       <c r="R19" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T19" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>5</v>
       </c>
       <c r="Q20" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R20" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="S20" t="s">
         <v>10</v>
@@ -1091,22 +1133,19 @@
       <c r="T20" t="s">
         <v>14</v>
       </c>
-      <c r="U20" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>13</v>
+      <c r="Z20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="s">
         <v>5</v>
@@ -1115,62 +1154,65 @@
         <v>7</v>
       </c>
       <c r="S21" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" t="s">
         <v>10</v>
       </c>
       <c r="U21" t="s">
         <v>14</v>
       </c>
-      <c r="V21" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" t="s">
-        <v>14</v>
-      </c>
-      <c r="X21" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>13</v>
+      <c r="AA21" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
+      <c r="Q22" t="s">
+        <v>5</v>
+      </c>
       <c r="R22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S22" t="s">
-        <v>7</v>
-      </c>
-      <c r="T22" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V22" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="W22" t="s">
+        <v>10</v>
+      </c>
+      <c r="X22" t="s">
+        <v>10</v>
       </c>
       <c r="Y22" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R23" t="s">
         <v>5</v>
@@ -1179,53 +1221,56 @@
         <v>7</v>
       </c>
       <c r="T23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA23" t="s">
+        <v>18</v>
+      </c>
+      <c r="U23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V23" t="s">
         <v>14</v>
       </c>
       <c r="AB23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>24</v>
-      </c>
-      <c r="B24">
-        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
+      <c r="R24" t="s">
+        <v>5</v>
+      </c>
       <c r="S24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="s">
-        <v>7</v>
-      </c>
-      <c r="U24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA24" t="s">
         <v>10</v>
       </c>
       <c r="AB24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1237,33 +1282,33 @@
         <v>7</v>
       </c>
       <c r="U25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W25" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>10</v>
       </c>
       <c r="AC25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="S26" t="s">
+        <v>5</v>
       </c>
       <c r="T26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="V26" t="s">
         <v>10</v>
@@ -1271,85 +1316,151 @@
       <c r="W26" t="s">
         <v>14</v>
       </c>
-      <c r="X26" t="s">
-        <v>13</v>
-      </c>
       <c r="AC26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="T27" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" t="s">
+        <v>7</v>
+      </c>
+      <c r="V27" t="s">
+        <v>18</v>
+      </c>
+      <c r="W27" t="s">
+        <v>10</v>
+      </c>
+      <c r="X27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="T27" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" t="s">
-        <v>7</v>
-      </c>
-      <c r="V27" t="s">
-        <v>10</v>
-      </c>
-      <c r="W27" t="s">
-        <v>14</v>
-      </c>
-      <c r="X27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>20</v>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s">
+        <v>5</v>
+      </c>
+      <c r="U28" t="s">
+        <v>7</v>
+      </c>
+      <c r="V28" t="s">
+        <v>18</v>
+      </c>
+      <c r="W28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X28" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/project/outputs_xlsx_solution/prog-loop.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.2-wide.xlsx
@@ -582,12 +582,6 @@
       <c r="AB1">
         <v>25</v>
       </c>
-      <c r="AC1">
-        <v>26</v>
-      </c>
-      <c r="AD1">
-        <v>27</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -803,15 +797,9 @@
         <v>18</v>
       </c>
       <c r="P9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>11</v>
-      </c>
-      <c r="R9" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -837,7 +825,7 @@
       <c r="K10" t="s">
         <v>14</v>
       </c>
-      <c r="S10" t="s">
+      <c r="Q10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -866,7 +854,7 @@
       <c r="L11" t="s">
         <v>14</v>
       </c>
-      <c r="T11" t="s">
+      <c r="R11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -887,15 +875,12 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R12" t="s">
         <v>15</v>
       </c>
     </row>
@@ -909,22 +894,19 @@
       <c r="C13" t="s">
         <v>9</v>
       </c>
+      <c r="L13" t="s">
+        <v>5</v>
+      </c>
       <c r="M13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
-      </c>
-      <c r="P13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>14</v>
-      </c>
-      <c r="U13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S13" t="s">
         <v>15</v>
       </c>
     </row>
@@ -938,14 +920,20 @@
       <c r="C14" t="s">
         <v>12</v>
       </c>
+      <c r="L14" t="s">
+        <v>5</v>
+      </c>
       <c r="M14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="P14" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" t="s">
         <v>10</v>
@@ -954,12 +942,6 @@
         <v>10</v>
       </c>
       <c r="S14" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -973,22 +955,19 @@
       <c r="C15" t="s">
         <v>13</v>
       </c>
+      <c r="M15" t="s">
+        <v>5</v>
+      </c>
       <c r="N15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>10</v>
-      </c>
-      <c r="R15" t="s">
-        <v>14</v>
-      </c>
-      <c r="V15" t="s">
+        <v>14</v>
+      </c>
+      <c r="T15" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1002,25 +981,25 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="M16" t="s">
+        <v>5</v>
+      </c>
       <c r="N16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O16" t="s">
-        <v>7</v>
-      </c>
-      <c r="P16" t="s">
         <v>18</v>
       </c>
+      <c r="S16" t="s">
+        <v>10</v>
+      </c>
+      <c r="T16" t="s">
+        <v>10</v>
+      </c>
       <c r="U16" t="s">
         <v>10</v>
       </c>
       <c r="V16" t="s">
-        <v>10</v>
-      </c>
-      <c r="W16" t="s">
-        <v>10</v>
-      </c>
-      <c r="X16" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1034,19 +1013,19 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
+      <c r="N17" t="s">
+        <v>5</v>
+      </c>
       <c r="O17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P17" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q17" t="s">
         <v>18</v>
       </c>
-      <c r="X17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y17" t="s">
+      <c r="V17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1060,22 +1039,19 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
+      <c r="N18" t="s">
+        <v>5</v>
+      </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="s">
-        <v>18</v>
-      </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y18" t="s">
+        <v>14</v>
+      </c>
+      <c r="W18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1089,22 +1065,19 @@
       <c r="C19" t="s">
         <v>20</v>
       </c>
+      <c r="O19" t="s">
+        <v>5</v>
+      </c>
       <c r="P19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19" t="s">
-        <v>18</v>
-      </c>
-      <c r="S19" t="s">
-        <v>10</v>
-      </c>
-      <c r="T19" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z19" t="s">
+        <v>14</v>
+      </c>
+      <c r="X19" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1118,22 +1091,19 @@
       <c r="C20" t="s">
         <v>21</v>
       </c>
+      <c r="O20" t="s">
+        <v>5</v>
+      </c>
       <c r="P20" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R20" t="s">
-        <v>18</v>
-      </c>
-      <c r="S20" t="s">
-        <v>10</v>
-      </c>
-      <c r="T20" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z20" t="s">
+        <v>14</v>
+      </c>
+      <c r="X20" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1147,22 +1117,19 @@
       <c r="C21" t="s">
         <v>9</v>
       </c>
+      <c r="P21" t="s">
+        <v>5</v>
+      </c>
       <c r="Q21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S21" t="s">
-        <v>18</v>
-      </c>
-      <c r="T21" t="s">
-        <v>10</v>
-      </c>
-      <c r="U21" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA21" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1176,14 +1143,20 @@
       <c r="C22" t="s">
         <v>12</v>
       </c>
+      <c r="P22" t="s">
+        <v>5</v>
+      </c>
       <c r="Q22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R22" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="S22" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="T22" t="s">
+        <v>10</v>
       </c>
       <c r="U22" t="s">
         <v>10</v>
@@ -1192,15 +1165,9 @@
         <v>10</v>
       </c>
       <c r="W22" t="s">
-        <v>10</v>
-      </c>
-      <c r="X22" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1214,22 +1181,19 @@
       <c r="C23" t="s">
         <v>13</v>
       </c>
+      <c r="Q23" t="s">
+        <v>5</v>
+      </c>
       <c r="R23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="s">
-        <v>18</v>
-      </c>
-      <c r="U23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V23" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB23" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1243,25 +1207,25 @@
       <c r="C24" t="s">
         <v>16</v>
       </c>
+      <c r="Q24" t="s">
+        <v>5</v>
+      </c>
       <c r="R24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S24" t="s">
-        <v>7</v>
-      </c>
-      <c r="T24" t="s">
         <v>18</v>
       </c>
+      <c r="W24" t="s">
+        <v>10</v>
+      </c>
+      <c r="X24" t="s">
+        <v>10</v>
+      </c>
       <c r="Y24" t="s">
         <v>10</v>
       </c>
       <c r="Z24" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB24" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1275,19 +1239,19 @@
       <c r="C25" t="s">
         <v>17</v>
       </c>
+      <c r="R25" t="s">
+        <v>5</v>
+      </c>
       <c r="S25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T25" t="s">
-        <v>7</v>
-      </c>
-      <c r="U25" t="s">
         <v>18</v>
       </c>
-      <c r="AB25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC25" t="s">
+      <c r="Z25" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA25" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1301,22 +1265,19 @@
       <c r="C26" t="s">
         <v>19</v>
       </c>
+      <c r="R26" t="s">
+        <v>5</v>
+      </c>
       <c r="S26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U26" t="s">
-        <v>18</v>
-      </c>
-      <c r="V26" t="s">
-        <v>10</v>
-      </c>
-      <c r="W26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA26" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1330,22 +1291,19 @@
       <c r="C27" t="s">
         <v>20</v>
       </c>
+      <c r="S27" t="s">
+        <v>5</v>
+      </c>
       <c r="T27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27" t="s">
-        <v>18</v>
-      </c>
-      <c r="W27" t="s">
-        <v>10</v>
-      </c>
-      <c r="X27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB27" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1359,22 +1317,19 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="S28" t="s">
+        <v>5</v>
+      </c>
       <c r="T28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28" t="s">
-        <v>18</v>
-      </c>
-      <c r="W28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD28" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB28" t="s">
         <v>15</v>
       </c>
     </row>
